--- a/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>332</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>17502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>111720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>40392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63024</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90625</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180611</t>
+          <t>171236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>34126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>74657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63626</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88660</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105722</t>
+          <t>103957</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155153</t>
+          <t>152840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40108</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67798</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>46080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>33637</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>43704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>54616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73375</t>
+          <t>73566</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>24785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48112</t>
+          <t>47534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138705</t>
+          <t>142816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118828</t>
+          <t>120755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211235</t>
+          <t>211300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112975</t>
+          <t>111808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>101797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>130137</t>
+          <t>129402</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>179567</t>
+          <t>171839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>234649</t>
+          <t>231045</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45261</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>64434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44331</t>
+          <t>44019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71728</t>
+          <t>71627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>882</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9134</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14213</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7508</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14497</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8818</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7628</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13076</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9163</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1731</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5027</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6728</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11331</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9185</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8648</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>47,1%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>11590</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>17329</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>39,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7378</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12045</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,43%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>43,15%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>12005</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>6815</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>17982</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25312</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25312</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25312</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23150</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23150</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23150</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>43674</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>43674</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>43674</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13363</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21259</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10135</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5125</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17502</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35526</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46382</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36740</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>64318</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40992</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111720</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>37677</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40392</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63216</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115666</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>70402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171236</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69060</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>58342</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80461</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33,22%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58938</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>34126</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>74657</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,81%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>42,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>58748</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64028</t>
+          <t>49681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88062</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>134334</t>
+          <t>127808</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103957</t>
+          <t>113278</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152840</t>
+          <t>143245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32088</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23560</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41491</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12181</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30352</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68184</t>
+          <t>67361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14704</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9290</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22696</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46080</t>
+          <t>45334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175596</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175596</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175596</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>174317</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>174317</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>174317</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>189390</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>189390</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>189390</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>363707</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>363707</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>363707</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3643</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3991</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1532</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8231</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6895</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11846</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4842</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2179</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9425</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36205</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43704</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64227</t>
+          <t>61901</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54616</t>
+          <t>52785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15430</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16846</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10060</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8976</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>58522</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>58522</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>58522</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>53255</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>53255</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>53255</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62968</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62968</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62968</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>116223</t>
+          <t>111524</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116223</t>
+          <t>111524</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116223</t>
+          <t>111524</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11365</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26633</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9317</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24785</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47534</t>
+          <t>45824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>62411</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>51807</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>75490</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>76668</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>51495</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>142816</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>30,58%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>37349</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120755</t>
+          <t>93215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211300</t>
+          <t>125524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>106593</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>91276</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>120418</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>94588</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>59422</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>111808</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>37,73%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>44,59%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101797</t>
+          <t>79915</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>103796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>209926</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>171839</t>
+          <t>181239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>231045</t>
+          <t>218146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>46515</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>35486</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>58749</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>23667</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>45024</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>44890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>81580</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64434</t>
+          <t>67132</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97281</t>
+          <t>96401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26023</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>28864</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>19604</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>39295</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>39690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>56745</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>44933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>69150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>250723</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>250723</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>250723</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>219623</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>219623</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>219623</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>530995</t>
+          <t>479052</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>530995</t>
+          <t>479052</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>530995</t>
+          <t>479052</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
